--- a/data/nzd0461/nzd0461.xlsx
+++ b/data/nzd0461/nzd0461.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N340"/>
+  <dimension ref="A1:N341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16698,6 +16698,54 @@
         <v>401.58</v>
       </c>
       <c r="N340" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:26:51+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>407.76</v>
+      </c>
+      <c r="C341" t="n">
+        <v>401.27</v>
+      </c>
+      <c r="D341" t="n">
+        <v>406.95</v>
+      </c>
+      <c r="E341" t="n">
+        <v>415.18</v>
+      </c>
+      <c r="F341" t="n">
+        <v>419.39</v>
+      </c>
+      <c r="G341" t="n">
+        <v>407.28</v>
+      </c>
+      <c r="H341" t="n">
+        <v>396.59</v>
+      </c>
+      <c r="I341" t="n">
+        <v>394.3</v>
+      </c>
+      <c r="J341" t="n">
+        <v>393.47</v>
+      </c>
+      <c r="K341" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="L341" t="n">
+        <v>403.56</v>
+      </c>
+      <c r="M341" t="n">
+        <v>401.91</v>
+      </c>
+      <c r="N341" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16714,7 +16762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20267,6 +20315,16 @@
       </c>
       <c r="B355" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -20435,28 +20493,28 @@
         <v>0.1696</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7755775674557032</v>
+        <v>0.7878930209162327</v>
       </c>
       <c r="J2" t="n">
+        <v>340</v>
+      </c>
+      <c r="K2" t="n">
         <v>339</v>
       </c>
-      <c r="K2" t="n">
-        <v>338</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.09157976049599281</v>
+        <v>0.09449650171727486</v>
       </c>
       <c r="M2" t="n">
-        <v>15.41737887553279</v>
+        <v>15.42589975895999</v>
       </c>
       <c r="N2" t="n">
-        <v>331.7096705090984</v>
+        <v>331.9712688217845</v>
       </c>
       <c r="O2" t="n">
-        <v>18.21289846534863</v>
+        <v>18.22007872710171</v>
       </c>
       <c r="P2" t="n">
-        <v>366.8530959664451</v>
+        <v>366.7307974744427</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20517,28 +20575,28 @@
         <v>0.1201</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9064813023266073</v>
+        <v>0.9191318980148413</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1217368814536117</v>
+        <v>0.1250372009810046</v>
       </c>
       <c r="M3" t="n">
-        <v>15.31337218432946</v>
+        <v>15.32894034846187</v>
       </c>
       <c r="N3" t="n">
-        <v>328.8870901563683</v>
+        <v>329.2295338509724</v>
       </c>
       <c r="O3" t="n">
-        <v>18.13524441953756</v>
+        <v>18.14468334942697</v>
       </c>
       <c r="P3" t="n">
-        <v>356.3417803067636</v>
+        <v>356.2159390386218</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20599,28 +20657,28 @@
         <v>0.1062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.177148520650785</v>
+        <v>1.191635054125032</v>
       </c>
       <c r="J4" t="n">
+        <v>340</v>
+      </c>
+      <c r="K4" t="n">
         <v>339</v>
       </c>
-      <c r="K4" t="n">
-        <v>338</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1949755357442542</v>
+        <v>0.1990605354092728</v>
       </c>
       <c r="M4" t="n">
-        <v>15.24648510645161</v>
+        <v>15.27008472536917</v>
       </c>
       <c r="N4" t="n">
-        <v>317.3101030159502</v>
+        <v>318.0924644429499</v>
       </c>
       <c r="O4" t="n">
-        <v>17.81320024633278</v>
+        <v>17.83514688593705</v>
       </c>
       <c r="P4" t="n">
-        <v>351.8827706335369</v>
+        <v>351.7384545731024</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20681,28 +20739,28 @@
         <v>0.1328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.096142077887545</v>
+        <v>1.111349711115507</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1745693367635006</v>
+        <v>0.1786900695871747</v>
       </c>
       <c r="M5" t="n">
-        <v>15.17616985078815</v>
+        <v>15.19922871498311</v>
       </c>
       <c r="N5" t="n">
-        <v>316.3298717617848</v>
+        <v>317.2877005453449</v>
       </c>
       <c r="O5" t="n">
-        <v>17.78566478267778</v>
+        <v>17.81257141867352</v>
       </c>
       <c r="P5" t="n">
-        <v>361.104280515848</v>
+        <v>360.9528793270957</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20763,28 +20821,28 @@
         <v>0.1398</v>
       </c>
       <c r="I6" t="n">
-        <v>1.150382409222429</v>
+        <v>1.163659040509751</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K6" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2031966308051887</v>
+        <v>0.2072267393723054</v>
       </c>
       <c r="M6" t="n">
-        <v>14.36854741486547</v>
+        <v>14.38277527737579</v>
       </c>
       <c r="N6" t="n">
-        <v>288.8614344750894</v>
+        <v>289.4475796656876</v>
       </c>
       <c r="O6" t="n">
-        <v>16.99592405475764</v>
+        <v>17.01315901488279</v>
       </c>
       <c r="P6" t="n">
-        <v>367.1478530658495</v>
+        <v>367.015483412711</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20841,28 +20899,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.140656632848469</v>
+        <v>1.153333189614073</v>
       </c>
       <c r="J7" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K7" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1954146416932208</v>
+        <v>0.199282075203063</v>
       </c>
       <c r="M7" t="n">
-        <v>14.9992860057249</v>
+        <v>15.01372378708937</v>
       </c>
       <c r="N7" t="n">
-        <v>297.5603303372661</v>
+        <v>297.9963283362908</v>
       </c>
       <c r="O7" t="n">
-        <v>17.24993711111047</v>
+        <v>17.26257015442054</v>
       </c>
       <c r="P7" t="n">
-        <v>356.2491478338667</v>
+        <v>356.1225427330588</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20919,28 +20977,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.16614358090735</v>
+        <v>1.176052727991971</v>
       </c>
       <c r="J8" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K8" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.192173652375321</v>
+        <v>0.1954853609835834</v>
       </c>
       <c r="M8" t="n">
-        <v>15.81311440075284</v>
+        <v>15.81060115576881</v>
       </c>
       <c r="N8" t="n">
-        <v>318.9706808542604</v>
+        <v>318.8300301592419</v>
       </c>
       <c r="O8" t="n">
-        <v>17.85975030212518</v>
+        <v>17.85581222345379</v>
       </c>
       <c r="P8" t="n">
-        <v>349.5107097891133</v>
+        <v>349.4124133549735</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20997,28 +21055,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.18786736350486</v>
+        <v>1.19897256747414</v>
       </c>
       <c r="J9" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1959508656131349</v>
+        <v>0.1994846528590393</v>
       </c>
       <c r="M9" t="n">
-        <v>15.87762357341742</v>
+        <v>15.88149808843543</v>
       </c>
       <c r="N9" t="n">
-        <v>323.1392528579422</v>
+        <v>323.1924683422068</v>
       </c>
       <c r="O9" t="n">
-        <v>17.97607445628612</v>
+        <v>17.97755457069194</v>
       </c>
       <c r="P9" t="n">
-        <v>344.6536209519672</v>
+        <v>344.5434891730904</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21075,28 +21133,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.288334582504792</v>
+        <v>1.302364445503472</v>
       </c>
       <c r="J10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K10" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2242395318917989</v>
+        <v>0.2283371982745169</v>
       </c>
       <c r="M10" t="n">
-        <v>15.68604135356356</v>
+        <v>15.70290580258987</v>
       </c>
       <c r="N10" t="n">
-        <v>322.286200604044</v>
+        <v>322.9511131526643</v>
       </c>
       <c r="O10" t="n">
-        <v>17.9523313417518</v>
+        <v>17.97084063567045</v>
       </c>
       <c r="P10" t="n">
-        <v>336.2855943598198</v>
+        <v>336.1467667892699</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21153,28 +21211,28 @@
         <v>0.1806</v>
       </c>
       <c r="I11" t="n">
-        <v>1.271115552454018</v>
+        <v>1.289039408470757</v>
       </c>
       <c r="J11" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K11" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2162112109042914</v>
+        <v>0.220781031831133</v>
       </c>
       <c r="M11" t="n">
-        <v>15.59566918508802</v>
+        <v>15.62895257542833</v>
       </c>
       <c r="N11" t="n">
-        <v>325.9811880798508</v>
+        <v>327.6438657403517</v>
       </c>
       <c r="O11" t="n">
-        <v>18.05494912980512</v>
+        <v>18.10093549351391</v>
       </c>
       <c r="P11" t="n">
-        <v>335.6452946674287</v>
+        <v>335.4673483283119</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21231,28 +21289,28 @@
         <v>0.1692</v>
       </c>
       <c r="I12" t="n">
-        <v>1.099037507394187</v>
+        <v>1.114852046903648</v>
       </c>
       <c r="J12" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K12" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1965018552822674</v>
+        <v>0.2009492730228706</v>
       </c>
       <c r="M12" t="n">
-        <v>14.34602557727021</v>
+        <v>14.37178773091789</v>
       </c>
       <c r="N12" t="n">
-        <v>275.5103404611676</v>
+        <v>276.7450905573352</v>
       </c>
       <c r="O12" t="n">
-        <v>16.59850416336266</v>
+        <v>16.63565720244726</v>
       </c>
       <c r="P12" t="n">
-        <v>348.36977981198</v>
+        <v>348.2128570150894</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21309,28 +21367,28 @@
         <v>0.1283</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5608385721486426</v>
+        <v>0.5743194281316719</v>
       </c>
       <c r="J13" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K13" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08225123582620508</v>
+        <v>0.08584164826928686</v>
       </c>
       <c r="M13" t="n">
-        <v>12.12211227978864</v>
+        <v>12.14410745646488</v>
       </c>
       <c r="N13" t="n">
-        <v>194.8393646438333</v>
+        <v>195.7469747330266</v>
       </c>
       <c r="O13" t="n">
-        <v>13.95848719037394</v>
+        <v>13.99096046499405</v>
       </c>
       <c r="P13" t="n">
-        <v>364.7821985689433</v>
+        <v>364.6475078064125</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21368,7 +21426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N340"/>
+  <dimension ref="A1:N341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45707,6 +45765,78 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:26:51+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-44.40598849866243,167.91820889235402</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-44.405598520738636,167.9189225367107</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-44.40512506554247,167.9195376570103</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-44.404647684148166,167.92010951837395</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-44.404255687730526,167.92056064553202</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-44.40381715636114,167.92099722560855</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-44.403282422102514,167.92150156946818</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-44.40272902791183,167.9219002505215</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-44.4021545495601,167.92221269916934</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-44.40153614388782,167.92244345173873</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-44.40094585959267,167.9226683635197</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-44.400357718523985,167.9228629893865</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0461/nzd0461.xlsx
+++ b/data/nzd0461/nzd0461.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N341"/>
+  <dimension ref="A1:N344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16748,6 +16748,150 @@
       <c r="N341" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:26:55+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>413.51</v>
+      </c>
+      <c r="C342" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="D342" t="n">
+        <v>399.01</v>
+      </c>
+      <c r="E342" t="n">
+        <v>407.95</v>
+      </c>
+      <c r="F342" t="n">
+        <v>419.39</v>
+      </c>
+      <c r="G342" t="n">
+        <v>407.66</v>
+      </c>
+      <c r="H342" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="I342" t="n">
+        <v>394.47</v>
+      </c>
+      <c r="J342" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="K342" t="n">
+        <v>397.11</v>
+      </c>
+      <c r="L342" t="n">
+        <v>402.99</v>
+      </c>
+      <c r="M342" t="n">
+        <v>400.3</v>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:33:05+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>418</v>
+      </c>
+      <c r="C343" t="n">
+        <v>408.59</v>
+      </c>
+      <c r="D343" t="n">
+        <v>402.71</v>
+      </c>
+      <c r="E343" t="n">
+        <v>411.57</v>
+      </c>
+      <c r="F343" t="n">
+        <v>422.88</v>
+      </c>
+      <c r="G343" t="n">
+        <v>409.96</v>
+      </c>
+      <c r="H343" t="n">
+        <v>400.49</v>
+      </c>
+      <c r="I343" t="n">
+        <v>397.59</v>
+      </c>
+      <c r="J343" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="K343" t="n">
+        <v>397.36</v>
+      </c>
+      <c r="L343" t="n">
+        <v>403.69</v>
+      </c>
+      <c r="M343" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:33:10+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>419.33</v>
+      </c>
+      <c r="C344" t="n">
+        <v>410.61</v>
+      </c>
+      <c r="D344" t="n">
+        <v>405.75</v>
+      </c>
+      <c r="E344" t="n">
+        <v>411.89</v>
+      </c>
+      <c r="F344" t="n">
+        <v>421.42</v>
+      </c>
+      <c r="G344" t="n">
+        <v>408.94</v>
+      </c>
+      <c r="H344" t="n">
+        <v>400.17</v>
+      </c>
+      <c r="I344" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="J344" t="n">
+        <v>393.75</v>
+      </c>
+      <c r="K344" t="n">
+        <v>395.99</v>
+      </c>
+      <c r="L344" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="M344" t="n">
+        <v>401.92</v>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16762,7 +16906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20325,6 +20469,36 @@
       </c>
       <c r="B356" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -20493,28 +20667,28 @@
         <v>0.1696</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7878930209162327</v>
+        <v>0.8396163739043984</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09449650171727486</v>
+        <v>0.1057203717945699</v>
       </c>
       <c r="M2" t="n">
-        <v>15.42589975895999</v>
+        <v>15.51680100065973</v>
       </c>
       <c r="N2" t="n">
-        <v>331.9712688217845</v>
+        <v>336.5574182110216</v>
       </c>
       <c r="O2" t="n">
-        <v>18.22007872710171</v>
+        <v>18.34550130716034</v>
       </c>
       <c r="P2" t="n">
-        <v>366.7307974744427</v>
+        <v>366.2160078110854</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20575,28 +20749,28 @@
         <v>0.1201</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9191318980148413</v>
+        <v>0.9675757028699041</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1250372009810046</v>
+        <v>0.1367207058867468</v>
       </c>
       <c r="M3" t="n">
-        <v>15.32894034846187</v>
+        <v>15.42514263368487</v>
       </c>
       <c r="N3" t="n">
-        <v>329.2295338509724</v>
+        <v>332.9327342078656</v>
       </c>
       <c r="O3" t="n">
-        <v>18.14468334942697</v>
+        <v>18.24644442645925</v>
       </c>
       <c r="P3" t="n">
-        <v>356.2159390386218</v>
+        <v>355.7329650153061</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20657,28 +20831,28 @@
         <v>0.1062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.191635054125032</v>
+        <v>1.22575317152163</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1990605354092728</v>
+        <v>0.2097958310843692</v>
       </c>
       <c r="M4" t="n">
-        <v>15.27008472536917</v>
+        <v>15.29541817150237</v>
       </c>
       <c r="N4" t="n">
-        <v>318.0924644429499</v>
+        <v>318.6098262691704</v>
       </c>
       <c r="O4" t="n">
-        <v>17.83514688593705</v>
+        <v>17.84964499000387</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7384545731024</v>
+        <v>351.3977797195711</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20739,28 +20913,28 @@
         <v>0.1328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.111349711115507</v>
+        <v>1.147081732551829</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1786900695871747</v>
+        <v>0.1894925521825799</v>
       </c>
       <c r="M5" t="n">
-        <v>15.19922871498311</v>
+        <v>15.22288785292527</v>
       </c>
       <c r="N5" t="n">
-        <v>317.2877005453449</v>
+        <v>318.0756650576182</v>
       </c>
       <c r="O5" t="n">
-        <v>17.81257141867352</v>
+        <v>17.83467591680932</v>
       </c>
       <c r="P5" t="n">
-        <v>360.9528793270957</v>
+        <v>360.5963427194287</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20821,28 +20995,28 @@
         <v>0.1398</v>
       </c>
       <c r="I6" t="n">
-        <v>1.163659040509751</v>
+        <v>1.205274145303749</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K6" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2072267393723054</v>
+        <v>0.2195559786150025</v>
       </c>
       <c r="M6" t="n">
-        <v>14.38277527737579</v>
+        <v>14.43327603632765</v>
       </c>
       <c r="N6" t="n">
-        <v>289.4475796656876</v>
+        <v>291.7400411157731</v>
       </c>
       <c r="O6" t="n">
-        <v>17.01315901488279</v>
+        <v>17.08039932541898</v>
       </c>
       <c r="P6" t="n">
-        <v>367.015483412711</v>
+        <v>366.5996596594006</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20899,28 +21073,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.153333189614073</v>
+        <v>1.192746032232525</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K7" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L7" t="n">
-        <v>0.199282075203063</v>
+        <v>0.2111039308626887</v>
       </c>
       <c r="M7" t="n">
-        <v>15.01372378708937</v>
+        <v>15.06272290128415</v>
       </c>
       <c r="N7" t="n">
-        <v>297.9963283362908</v>
+        <v>299.7149261670914</v>
       </c>
       <c r="O7" t="n">
-        <v>17.26257015442054</v>
+        <v>17.31227674706858</v>
       </c>
       <c r="P7" t="n">
-        <v>356.1225427330588</v>
+        <v>355.7280495330697</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20977,28 +21151,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.176052727991971</v>
+        <v>1.209167787849825</v>
       </c>
       <c r="J8" t="n">
+        <v>343</v>
+      </c>
+      <c r="K8" t="n">
         <v>340</v>
       </c>
-      <c r="K8" t="n">
-        <v>337</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1954853609835834</v>
+        <v>0.2060556000212267</v>
       </c>
       <c r="M8" t="n">
-        <v>15.81060115576881</v>
+        <v>15.81742774775976</v>
       </c>
       <c r="N8" t="n">
-        <v>318.8300301592419</v>
+        <v>319.1038635809522</v>
       </c>
       <c r="O8" t="n">
-        <v>17.85581222345379</v>
+        <v>17.86347848491307</v>
       </c>
       <c r="P8" t="n">
-        <v>349.4124133549735</v>
+        <v>349.0831835592672</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21055,28 +21229,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.19897256747414</v>
+        <v>1.234501116674405</v>
       </c>
       <c r="J9" t="n">
+        <v>343</v>
+      </c>
+      <c r="K9" t="n">
         <v>340</v>
       </c>
-      <c r="K9" t="n">
-        <v>337</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1994846528590393</v>
+        <v>0.2104802520255524</v>
       </c>
       <c r="M9" t="n">
-        <v>15.88149808843543</v>
+        <v>15.90224474592306</v>
       </c>
       <c r="N9" t="n">
-        <v>323.1924683422068</v>
+        <v>323.8819519404546</v>
       </c>
       <c r="O9" t="n">
-        <v>17.97755457069194</v>
+        <v>17.99672058849763</v>
       </c>
       <c r="P9" t="n">
-        <v>344.5434891730904</v>
+        <v>344.1903688162531</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21133,28 +21307,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.302364445503472</v>
+        <v>1.343420544535288</v>
       </c>
       <c r="J10" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K10" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2283371982745169</v>
+        <v>0.2404313114186798</v>
       </c>
       <c r="M10" t="n">
-        <v>15.70290580258987</v>
+        <v>15.74780902334741</v>
       </c>
       <c r="N10" t="n">
-        <v>322.9511131526643</v>
+        <v>324.8282591924327</v>
       </c>
       <c r="O10" t="n">
-        <v>17.97084063567045</v>
+        <v>18.02299251490808</v>
       </c>
       <c r="P10" t="n">
-        <v>336.1467667892699</v>
+        <v>335.7396192195624</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21211,28 +21385,28 @@
         <v>0.1806</v>
       </c>
       <c r="I11" t="n">
-        <v>1.289039408470757</v>
+        <v>1.337305683825274</v>
       </c>
       <c r="J11" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K11" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L11" t="n">
-        <v>0.220781031831133</v>
+        <v>0.2337426747996358</v>
       </c>
       <c r="M11" t="n">
-        <v>15.62895257542833</v>
+        <v>15.70441679221209</v>
       </c>
       <c r="N11" t="n">
-        <v>327.6438657403517</v>
+        <v>331.2514005654349</v>
       </c>
       <c r="O11" t="n">
-        <v>18.10093549351391</v>
+        <v>18.20031319965222</v>
       </c>
       <c r="P11" t="n">
-        <v>335.4673483283119</v>
+        <v>334.9871413124731</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21289,28 +21463,28 @@
         <v>0.1692</v>
       </c>
       <c r="I12" t="n">
-        <v>1.114852046903648</v>
+        <v>1.159244011353349</v>
       </c>
       <c r="J12" t="n">
+        <v>343</v>
+      </c>
+      <c r="K12" t="n">
         <v>340</v>
       </c>
-      <c r="K12" t="n">
-        <v>337</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2009492730228706</v>
+        <v>0.2138102630583867</v>
       </c>
       <c r="M12" t="n">
-        <v>14.37178773091789</v>
+        <v>14.43412549707506</v>
       </c>
       <c r="N12" t="n">
-        <v>276.7450905573352</v>
+        <v>279.8156599307417</v>
       </c>
       <c r="O12" t="n">
-        <v>16.63565720244726</v>
+        <v>16.72769141067415</v>
       </c>
       <c r="P12" t="n">
-        <v>348.2128570150894</v>
+        <v>347.7714268605496</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21367,28 +21541,28 @@
         <v>0.1283</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5743194281316719</v>
+        <v>0.6125313202008578</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K13" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08584164826928686</v>
+        <v>0.09643535402004411</v>
       </c>
       <c r="M13" t="n">
-        <v>12.14410745646488</v>
+        <v>12.20129998314277</v>
       </c>
       <c r="N13" t="n">
-        <v>195.7469747330266</v>
+        <v>198.0878355134632</v>
       </c>
       <c r="O13" t="n">
-        <v>13.99096046499405</v>
+        <v>14.07436803247177</v>
       </c>
       <c r="P13" t="n">
-        <v>364.6475078064125</v>
+        <v>364.2648806900311</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21426,7 +21600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N341"/>
+  <dimension ref="A1:N344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45837,6 +46011,222 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:26:55+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-44.40594905922409,167.91816234243998</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-44.40557327962379,167.9188927447111</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-44.405179525749105,167.9196019364953</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-44.40469588225801,167.92017027045938</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-44.404255687730526,167.92056064553202</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-44.403815562938966,167.9209930135099</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-44.40328149960359,167.9214991308994</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-44.40272837091982,167.9218983270975</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-44.402154446829485,167.92221235156453</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-44.40154195196376,167.92246383269259</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-44.40094745549021,167.92267515136032</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-44.40036136880889,167.92288251355808</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:33:05+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-44.40591826215568,167.918125993072</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-44.40554831286232,167.91886327656255</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-44.40515414757103,167.91957198256438</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-44.40467174987457,167.92013985239035</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-44.40423687450026,167.92052565189007</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-44.40380591853844,167.92096751923378</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-44.403266068705264,167.92145834030612</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-44.402716313178466,167.92186302661787</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-44.40215266616519,167.9222063264148</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-44.401541122238825,167.92246092112748</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-44.400945495615986,167.92266681541577</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-44.400357287744825,167.9228606852919</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:33:10+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-44.405909139636854,167.91811522589458</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-44.40553445767869,167.91884692336998</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-44.40513329630616,167.91954737178634</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-44.40466961662486,167.92013716350144</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-44.40424474479263,167.92054029106126</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-44.40381019562106,167.92097882538994</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-44.403267410523036,167.92146188731334</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-44.40271955949446,167.92187253059163</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-44.40215359074093,167.92220945485786</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-44.40154566913054,167.9224768765053</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-44.40095106725689,167.92269051331687</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-44.400357695851405,167.92286286811836</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0461/nzd0461.xlsx
+++ b/data/nzd0461/nzd0461.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N344"/>
+  <dimension ref="A1:N347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16892,6 +16892,150 @@
       <c r="N344" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>421.41</v>
+      </c>
+      <c r="C345" t="n">
+        <v>413.85</v>
+      </c>
+      <c r="D345" t="n">
+        <v>409.61</v>
+      </c>
+      <c r="E345" t="n">
+        <v>414.22</v>
+      </c>
+      <c r="F345" t="n">
+        <v>422.91</v>
+      </c>
+      <c r="G345" t="n">
+        <v>410.15</v>
+      </c>
+      <c r="H345" t="n">
+        <v>401.49</v>
+      </c>
+      <c r="I345" t="n">
+        <v>398.55</v>
+      </c>
+      <c r="J345" t="n">
+        <v>395.29</v>
+      </c>
+      <c r="K345" t="n">
+        <v>397.25</v>
+      </c>
+      <c r="L345" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="M345" t="n">
+        <v>403.13</v>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-05 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>420.55</v>
+      </c>
+      <c r="C346" t="n">
+        <v>415.11</v>
+      </c>
+      <c r="D346" t="n">
+        <v>411.43</v>
+      </c>
+      <c r="E346" t="n">
+        <v>415.76</v>
+      </c>
+      <c r="F346" t="n">
+        <v>423.42</v>
+      </c>
+      <c r="G346" t="n">
+        <v>410.55</v>
+      </c>
+      <c r="H346" t="n">
+        <v>402.21</v>
+      </c>
+      <c r="I346" t="n">
+        <v>399.09</v>
+      </c>
+      <c r="J346" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="K346" t="n">
+        <v>397.72</v>
+      </c>
+      <c r="L346" t="n">
+        <v>402.88</v>
+      </c>
+      <c r="M346" t="n">
+        <v>403.64</v>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>420.55</v>
+      </c>
+      <c r="C347" t="n">
+        <v>419.8</v>
+      </c>
+      <c r="D347" t="n">
+        <v>415.69</v>
+      </c>
+      <c r="E347" t="n">
+        <v>418.97</v>
+      </c>
+      <c r="F347" t="n">
+        <v>423.42</v>
+      </c>
+      <c r="G347" t="n">
+        <v>410.55</v>
+      </c>
+      <c r="H347" t="n">
+        <v>403.03</v>
+      </c>
+      <c r="I347" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="J347" t="n">
+        <v>396.67</v>
+      </c>
+      <c r="K347" t="n">
+        <v>397.62</v>
+      </c>
+      <c r="L347" t="n">
+        <v>402.75</v>
+      </c>
+      <c r="M347" t="n">
+        <v>403.43</v>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16906,7 +17050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20499,6 +20643,36 @@
       </c>
       <c r="B359" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-01-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -20667,28 +20841,28 @@
         <v>0.1696</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8396163739043984</v>
+        <v>0.8952722407737889</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1057203717945699</v>
+        <v>0.1177607161383516</v>
       </c>
       <c r="M2" t="n">
-        <v>15.51680100065973</v>
+        <v>15.62415266405371</v>
       </c>
       <c r="N2" t="n">
-        <v>336.5574182110216</v>
+        <v>342.5883235473326</v>
       </c>
       <c r="O2" t="n">
-        <v>18.34550130716034</v>
+        <v>18.50914162102966</v>
       </c>
       <c r="P2" t="n">
-        <v>366.2160078110854</v>
+        <v>365.6606683707374</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20749,28 +20923,28 @@
         <v>0.1201</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9675757028699041</v>
+        <v>1.027481794240766</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1367207058867468</v>
+        <v>0.1500384705299231</v>
       </c>
       <c r="M3" t="n">
-        <v>15.42514263368487</v>
+        <v>15.57282901792514</v>
       </c>
       <c r="N3" t="n">
-        <v>332.9327342078656</v>
+        <v>340.48287792096</v>
       </c>
       <c r="O3" t="n">
-        <v>18.24644442645925</v>
+        <v>18.45217813486961</v>
       </c>
       <c r="P3" t="n">
-        <v>355.7329650153061</v>
+        <v>355.1341605571828</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20831,28 +21005,28 @@
         <v>0.1062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.22575317152163</v>
+        <v>1.274687759906185</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2097958310843692</v>
+        <v>0.222653551019812</v>
       </c>
       <c r="M4" t="n">
-        <v>15.29541817150237</v>
+        <v>15.39198702037521</v>
       </c>
       <c r="N4" t="n">
-        <v>318.6098262691704</v>
+        <v>322.8240689919259</v>
       </c>
       <c r="O4" t="n">
-        <v>17.84964499000387</v>
+        <v>17.96730555737075</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3977797195711</v>
+        <v>350.9079119527147</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20913,28 +21087,28 @@
         <v>0.1328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.147081732551829</v>
+        <v>1.190912085000023</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1894925521825799</v>
+        <v>0.2015769976607439</v>
       </c>
       <c r="M5" t="n">
-        <v>15.22288785292527</v>
+        <v>15.28177091094821</v>
       </c>
       <c r="N5" t="n">
-        <v>318.0756650576182</v>
+        <v>320.8954151166324</v>
       </c>
       <c r="O5" t="n">
-        <v>17.83467591680932</v>
+        <v>17.91355394991827</v>
       </c>
       <c r="P5" t="n">
-        <v>360.5963427194287</v>
+        <v>360.1578426940297</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20995,28 +21169,28 @@
         <v>0.1398</v>
       </c>
       <c r="I6" t="n">
-        <v>1.205274145303749</v>
+        <v>1.248127003935681</v>
       </c>
       <c r="J6" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2195559786150025</v>
+        <v>0.231974428736422</v>
       </c>
       <c r="M6" t="n">
-        <v>14.43327603632765</v>
+        <v>14.49193578926632</v>
       </c>
       <c r="N6" t="n">
-        <v>291.7400411157731</v>
+        <v>294.5081832196043</v>
       </c>
       <c r="O6" t="n">
-        <v>17.08039932541898</v>
+        <v>17.16124072494772</v>
       </c>
       <c r="P6" t="n">
-        <v>366.5996596594006</v>
+        <v>366.1703330484945</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21073,28 +21247,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.192746032232525</v>
+        <v>1.232722346487481</v>
       </c>
       <c r="J7" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2111039308626887</v>
+        <v>0.2229678703569308</v>
       </c>
       <c r="M7" t="n">
-        <v>15.06272290128415</v>
+        <v>15.11338677989544</v>
       </c>
       <c r="N7" t="n">
-        <v>299.7149261670914</v>
+        <v>301.7312495119194</v>
       </c>
       <c r="O7" t="n">
-        <v>17.31227674706858</v>
+        <v>17.37041304954834</v>
       </c>
       <c r="P7" t="n">
-        <v>355.7280495330697</v>
+        <v>355.3268541591283</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21151,28 +21325,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.209167787849825</v>
+        <v>1.2457643945279</v>
       </c>
       <c r="J8" t="n">
+        <v>346</v>
+      </c>
+      <c r="K8" t="n">
         <v>343</v>
       </c>
-      <c r="K8" t="n">
-        <v>340</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2060556000212267</v>
+        <v>0.2172237760253756</v>
       </c>
       <c r="M8" t="n">
-        <v>15.81742774775976</v>
+        <v>15.83839801138658</v>
       </c>
       <c r="N8" t="n">
-        <v>319.1038635809522</v>
+        <v>320.2026365321375</v>
       </c>
       <c r="O8" t="n">
-        <v>17.86347848491307</v>
+        <v>17.8942067868944</v>
       </c>
       <c r="P8" t="n">
-        <v>349.0831835592672</v>
+        <v>348.7183893428919</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21229,28 +21403,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.234501116674405</v>
+        <v>1.273138039733883</v>
       </c>
       <c r="J9" t="n">
+        <v>346</v>
+      </c>
+      <c r="K9" t="n">
         <v>343</v>
       </c>
-      <c r="K9" t="n">
-        <v>340</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.2104802520255524</v>
+        <v>0.2219623410902321</v>
       </c>
       <c r="M9" t="n">
-        <v>15.90224474592306</v>
+        <v>15.93553389707728</v>
       </c>
       <c r="N9" t="n">
-        <v>323.8819519404546</v>
+        <v>325.3839322341822</v>
       </c>
       <c r="O9" t="n">
-        <v>17.99672058849763</v>
+        <v>18.03840159865009</v>
       </c>
       <c r="P9" t="n">
-        <v>344.1903688162531</v>
+        <v>343.8053400938475</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21307,28 +21481,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.343420544535288</v>
+        <v>1.386184978959654</v>
       </c>
       <c r="J10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K10" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2404313114186798</v>
+        <v>0.2526353923825244</v>
       </c>
       <c r="M10" t="n">
-        <v>15.74780902334741</v>
+        <v>15.79900825354166</v>
       </c>
       <c r="N10" t="n">
-        <v>324.8282591924327</v>
+        <v>327.3179557355235</v>
       </c>
       <c r="O10" t="n">
-        <v>18.02299251490808</v>
+        <v>18.09193068015472</v>
       </c>
       <c r="P10" t="n">
-        <v>335.7396192195624</v>
+        <v>335.3143846086556</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21385,28 +21559,28 @@
         <v>0.1806</v>
       </c>
       <c r="I11" t="n">
-        <v>1.337305683825274</v>
+        <v>1.38420587332954</v>
       </c>
       <c r="J11" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K11" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2337426747996358</v>
+        <v>0.2463848098262943</v>
       </c>
       <c r="M11" t="n">
-        <v>15.70441679221209</v>
+        <v>15.77160561266346</v>
       </c>
       <c r="N11" t="n">
-        <v>331.2514005654349</v>
+        <v>334.7237993204363</v>
       </c>
       <c r="O11" t="n">
-        <v>18.20031319965222</v>
+        <v>18.29545843427916</v>
       </c>
       <c r="P11" t="n">
-        <v>334.9871413124731</v>
+        <v>334.5192778109993</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21463,28 +21637,28 @@
         <v>0.1692</v>
       </c>
       <c r="I12" t="n">
-        <v>1.159244011353349</v>
+        <v>1.201134412648232</v>
       </c>
       <c r="J12" t="n">
+        <v>346</v>
+      </c>
+      <c r="K12" t="n">
         <v>343</v>
       </c>
-      <c r="K12" t="n">
-        <v>340</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2138102630583867</v>
+        <v>0.2262215516555182</v>
       </c>
       <c r="M12" t="n">
-        <v>14.43412549707506</v>
+        <v>14.48417816727636</v>
       </c>
       <c r="N12" t="n">
-        <v>279.8156599307417</v>
+        <v>282.4604036770036</v>
       </c>
       <c r="O12" t="n">
-        <v>16.72769141067415</v>
+        <v>16.80655835312524</v>
       </c>
       <c r="P12" t="n">
-        <v>347.7714268605496</v>
+        <v>347.353750191165</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21541,28 +21715,28 @@
         <v>0.1283</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6125313202008578</v>
+        <v>0.6521118536374789</v>
       </c>
       <c r="J13" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K13" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09643535402004411</v>
+        <v>0.1075872583724194</v>
       </c>
       <c r="M13" t="n">
-        <v>12.20129998314277</v>
+        <v>12.26450958173389</v>
       </c>
       <c r="N13" t="n">
-        <v>198.0878355134632</v>
+        <v>200.8837293970891</v>
       </c>
       <c r="O13" t="n">
-        <v>14.07436803247177</v>
+        <v>14.17334573758395</v>
       </c>
       <c r="P13" t="n">
-        <v>364.2648806900311</v>
+        <v>363.8675027343133</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21600,7 +21774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N344"/>
+  <dimension ref="A1:N347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46227,6 +46401,222 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-44.40589487283874,167.9180983870072</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-44.40551223450865,167.9188206935128</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-44.4051068206804,167.91951612259976</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-44.40465408389879,167.92011758503514</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-44.40423671278191,167.92052535108522</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-44.403805121826856,167.9209654131853</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-44.403261875524,167.92144725590967</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-44.40271260310213,167.9218521649349</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-44.402148317233895,167.92219161114687</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-44.4015414873178,167.9224622022161</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-44.40094882740183,167.92268098652187</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-44.40035495246744,167.92284819467446</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-05 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-44.405900771611286,167.9181053492385</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-44.405503592163356,167.9188104930181</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-44.40509433735171,167.91950138853701</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-44.4046438176319,167.92010464476695</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-44.404233963569766,167.9205202374031</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-44.403803444539186,167.92096097939913</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-44.40325885643288,167.92143927514525</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-44.402710516183774,167.92184605523886</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-44.40214526955651,167.9221812988739</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-44.40153992743482,167.9224567284739</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-44.400947763470384,167.92267646129451</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-44.400353796164545,167.9228420100002</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-44.405900771611286,167.9181053492385</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-44.40547142342675,167.9187725245363</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-44.40506511812542,167.91946690113983</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-44.40462241846111,167.9200776718848</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-44.404233963569766,167.9205202374031</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-44.403803444539186,167.92096097939913</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-44.403255418022894,167.92143018594237</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-44.40270703798582,167.92183587241317</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-44.40214359162141,167.92217562133084</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-44.40154025932485,167.92245789309987</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-44.40094812744695,167.9226780093986</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-44.40035427228931,167.92284455663074</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0461/nzd0461.xlsx
+++ b/data/nzd0461/nzd0461.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N347"/>
+  <dimension ref="A1:N353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>420.55</v>
+        <v>424.78</v>
       </c>
       <c r="C347" t="n">
         <v>419.8</v>
@@ -17036,6 +17036,294 @@
       <c r="N347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>427.03</v>
+      </c>
+      <c r="C348" t="n">
+        <v>421.4</v>
+      </c>
+      <c r="D348" t="n">
+        <v>415.87</v>
+      </c>
+      <c r="E348" t="n">
+        <v>418.97</v>
+      </c>
+      <c r="F348" t="n">
+        <v>423.42</v>
+      </c>
+      <c r="G348" t="n">
+        <v>410.31</v>
+      </c>
+      <c r="H348" t="n">
+        <v>403.02</v>
+      </c>
+      <c r="I348" t="n">
+        <v>399.44</v>
+      </c>
+      <c r="J348" t="n">
+        <v>396.23</v>
+      </c>
+      <c r="K348" t="n">
+        <v>397.53</v>
+      </c>
+      <c r="L348" t="n">
+        <v>401.89</v>
+      </c>
+      <c r="M348" t="n">
+        <v>402.61</v>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-29 22:32:59+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>429.52</v>
+      </c>
+      <c r="C349" t="n">
+        <v>423.18</v>
+      </c>
+      <c r="D349" t="n">
+        <v>417.67</v>
+      </c>
+      <c r="E349" t="n">
+        <v>420.64</v>
+      </c>
+      <c r="F349" t="n">
+        <v>423.96</v>
+      </c>
+      <c r="G349" t="n">
+        <v>411.04</v>
+      </c>
+      <c r="H349" t="n">
+        <v>403.21</v>
+      </c>
+      <c r="I349" t="n">
+        <v>399.64</v>
+      </c>
+      <c r="J349" t="n">
+        <v>396.51</v>
+      </c>
+      <c r="K349" t="n">
+        <v>397.54</v>
+      </c>
+      <c r="L349" t="n">
+        <v>401.37</v>
+      </c>
+      <c r="M349" t="n">
+        <v>402.14</v>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-30 22:26:37+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>431.53</v>
+      </c>
+      <c r="C350" t="n">
+        <v>425.44</v>
+      </c>
+      <c r="D350" t="n">
+        <v>419.55</v>
+      </c>
+      <c r="E350" t="n">
+        <v>422.67</v>
+      </c>
+      <c r="F350" t="n">
+        <v>426.71</v>
+      </c>
+      <c r="G350" t="n">
+        <v>412.42</v>
+      </c>
+      <c r="H350" t="n">
+        <v>403.59</v>
+      </c>
+      <c r="I350" t="n">
+        <v>400.56</v>
+      </c>
+      <c r="J350" t="n">
+        <v>396.74</v>
+      </c>
+      <c r="K350" t="n">
+        <v>398.22</v>
+      </c>
+      <c r="L350" t="n">
+        <v>401.43</v>
+      </c>
+      <c r="M350" t="n">
+        <v>401.88</v>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>432.47</v>
+      </c>
+      <c r="C351" t="n">
+        <v>425.21</v>
+      </c>
+      <c r="D351" t="n">
+        <v>419.38</v>
+      </c>
+      <c r="E351" t="n">
+        <v>423.38</v>
+      </c>
+      <c r="F351" t="n">
+        <v>427.73</v>
+      </c>
+      <c r="G351" t="n">
+        <v>413.85</v>
+      </c>
+      <c r="H351" t="n">
+        <v>403.64</v>
+      </c>
+      <c r="I351" t="n">
+        <v>401.59</v>
+      </c>
+      <c r="J351" t="n">
+        <v>397.57</v>
+      </c>
+      <c r="K351" t="n">
+        <v>398.28</v>
+      </c>
+      <c r="L351" t="n">
+        <v>401.54</v>
+      </c>
+      <c r="M351" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-14 22:32:56+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>432.53</v>
+      </c>
+      <c r="C352" t="n">
+        <v>424.27</v>
+      </c>
+      <c r="D352" t="n">
+        <v>419.92</v>
+      </c>
+      <c r="E352" t="n">
+        <v>423.93</v>
+      </c>
+      <c r="F352" t="n">
+        <v>428.07</v>
+      </c>
+      <c r="G352" t="n">
+        <v>414.2</v>
+      </c>
+      <c r="H352" t="n">
+        <v>402.75</v>
+      </c>
+      <c r="I352" t="n">
+        <v>401.52</v>
+      </c>
+      <c r="J352" t="n">
+        <v>396.9</v>
+      </c>
+      <c r="K352" t="n">
+        <v>396.87</v>
+      </c>
+      <c r="L352" t="n">
+        <v>401.08</v>
+      </c>
+      <c r="M352" t="n">
+        <v>401.27</v>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>432.53</v>
+      </c>
+      <c r="C353" t="n">
+        <v>423.18</v>
+      </c>
+      <c r="D353" t="n">
+        <v>419.78</v>
+      </c>
+      <c r="E353" t="n">
+        <v>424.6</v>
+      </c>
+      <c r="F353" t="n">
+        <v>428.62</v>
+      </c>
+      <c r="G353" t="n">
+        <v>415.12</v>
+      </c>
+      <c r="H353" t="n">
+        <v>403.77</v>
+      </c>
+      <c r="I353" t="n">
+        <v>402.33</v>
+      </c>
+      <c r="J353" t="n">
+        <v>397.58</v>
+      </c>
+      <c r="K353" t="n">
+        <v>397.29</v>
+      </c>
+      <c r="L353" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="M353" t="n">
+        <v>401.27</v>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17050,7 +17338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20673,6 +20961,66 @@
       </c>
       <c r="B362" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-01-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-01-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-02-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -20841,28 +21189,28 @@
         <v>0.1696</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8952722407737889</v>
+        <v>1.033479008884517</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1177607161383516</v>
+        <v>0.1453527988358443</v>
       </c>
       <c r="M2" t="n">
-        <v>15.62415266405371</v>
+        <v>15.95155951083258</v>
       </c>
       <c r="N2" t="n">
-        <v>342.5883235473326</v>
+        <v>365.6514048568629</v>
       </c>
       <c r="O2" t="n">
-        <v>18.50914162102966</v>
+        <v>19.1220136193044</v>
       </c>
       <c r="P2" t="n">
-        <v>365.6606683707374</v>
+        <v>364.2764129388156</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20923,28 +21271,28 @@
         <v>0.1201</v>
       </c>
       <c r="I3" t="n">
-        <v>1.027481794240766</v>
+        <v>1.162802422850837</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1500384705299231</v>
+        <v>0.1780713888906282</v>
       </c>
       <c r="M3" t="n">
-        <v>15.57282901792514</v>
+        <v>15.92710120302813</v>
       </c>
       <c r="N3" t="n">
-        <v>340.48287792096</v>
+        <v>362.5806137735648</v>
       </c>
       <c r="O3" t="n">
-        <v>18.45217813486961</v>
+        <v>19.04154966838479</v>
       </c>
       <c r="P3" t="n">
-        <v>355.1341605571828</v>
+        <v>353.7765103076541</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21005,28 +21353,28 @@
         <v>0.1062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.274687759906185</v>
+        <v>1.386131823915293</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.222653551019812</v>
+        <v>0.2491420904991236</v>
       </c>
       <c r="M4" t="n">
-        <v>15.39198702037521</v>
+        <v>15.64278259784382</v>
       </c>
       <c r="N4" t="n">
-        <v>322.8240689919259</v>
+        <v>336.2481198813605</v>
       </c>
       <c r="O4" t="n">
-        <v>17.96730555737075</v>
+        <v>18.33706955544861</v>
       </c>
       <c r="P4" t="n">
-        <v>350.9079119527147</v>
+        <v>349.7881077575113</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21087,28 +21435,28 @@
         <v>0.1328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.190912085000023</v>
+        <v>1.291637345515896</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2015769976607439</v>
+        <v>0.2270952527120869</v>
       </c>
       <c r="M5" t="n">
-        <v>15.28177091094821</v>
+        <v>15.45944606214228</v>
       </c>
       <c r="N5" t="n">
-        <v>320.8954151166324</v>
+        <v>330.9184203312223</v>
       </c>
       <c r="O5" t="n">
-        <v>17.91355394991827</v>
+        <v>18.19116324843528</v>
       </c>
       <c r="P5" t="n">
-        <v>360.1578426940297</v>
+        <v>359.14629033991</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21169,28 +21517,28 @@
         <v>0.1398</v>
       </c>
       <c r="I6" t="n">
-        <v>1.248127003935681</v>
+        <v>1.337620689240584</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.231974428736422</v>
+        <v>0.2567527300659042</v>
       </c>
       <c r="M6" t="n">
-        <v>14.49193578926632</v>
+        <v>14.6273404382409</v>
       </c>
       <c r="N6" t="n">
-        <v>294.5081832196043</v>
+        <v>301.718177912334</v>
       </c>
       <c r="O6" t="n">
-        <v>17.16124072494772</v>
+        <v>17.37003678500233</v>
       </c>
       <c r="P6" t="n">
-        <v>366.1703330484945</v>
+        <v>365.2702375239318</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21247,28 +21595,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.232722346487481</v>
+        <v>1.314414252843027</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2229678703569308</v>
+        <v>0.246608562182879</v>
       </c>
       <c r="M7" t="n">
-        <v>15.11338677989544</v>
+        <v>15.21662978237187</v>
       </c>
       <c r="N7" t="n">
-        <v>301.7312495119194</v>
+        <v>306.7768667107202</v>
       </c>
       <c r="O7" t="n">
-        <v>17.37041304954834</v>
+        <v>17.51504686578715</v>
       </c>
       <c r="P7" t="n">
-        <v>355.3268541591283</v>
+        <v>354.5038199436373</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21325,28 +21673,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2457643945279</v>
+        <v>1.316821737130574</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2172237760253756</v>
+        <v>0.2390964583703701</v>
       </c>
       <c r="M8" t="n">
-        <v>15.83839801138658</v>
+        <v>15.86739229243819</v>
       </c>
       <c r="N8" t="n">
-        <v>320.2026365321375</v>
+        <v>322.4099261941785</v>
       </c>
       <c r="O8" t="n">
-        <v>17.8942067868944</v>
+        <v>17.95577695880015</v>
       </c>
       <c r="P8" t="n">
-        <v>348.7183893428919</v>
+        <v>348.0074183335261</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21403,28 +21751,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.273138039733883</v>
+        <v>1.349779614527609</v>
       </c>
       <c r="J9" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2219623410902321</v>
+        <v>0.2446211473984454</v>
       </c>
       <c r="M9" t="n">
-        <v>15.93553389707728</v>
+        <v>15.9946559978947</v>
       </c>
       <c r="N9" t="n">
-        <v>325.3839322341822</v>
+        <v>328.7754555237232</v>
       </c>
       <c r="O9" t="n">
-        <v>18.03840159865009</v>
+        <v>18.13216632186356</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8053400938475</v>
+        <v>343.0386583862498</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21481,28 +21829,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.386184978959654</v>
+        <v>1.467942079607077</v>
       </c>
       <c r="J10" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K10" t="n">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2526353923825244</v>
+        <v>0.2760844729678806</v>
       </c>
       <c r="M10" t="n">
-        <v>15.79900825354166</v>
+        <v>15.87907232219422</v>
       </c>
       <c r="N10" t="n">
-        <v>327.3179557355235</v>
+        <v>331.9403248283732</v>
       </c>
       <c r="O10" t="n">
-        <v>18.09193068015472</v>
+        <v>18.21922953443348</v>
       </c>
       <c r="P10" t="n">
-        <v>335.3143846086556</v>
+        <v>334.4983044714687</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21559,28 +21907,28 @@
         <v>0.1806</v>
       </c>
       <c r="I11" t="n">
-        <v>1.38420587332954</v>
+        <v>1.471096301593646</v>
       </c>
       <c r="J11" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K11" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2463848098262943</v>
+        <v>0.2703245596038756</v>
       </c>
       <c r="M11" t="n">
-        <v>15.77160561266346</v>
+        <v>15.8704051245337</v>
       </c>
       <c r="N11" t="n">
-        <v>334.7237993204363</v>
+        <v>340.4793869395606</v>
       </c>
       <c r="O11" t="n">
-        <v>18.29545843427916</v>
+        <v>18.4520835392527</v>
       </c>
       <c r="P11" t="n">
-        <v>334.5192778109993</v>
+        <v>333.6492253533823</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21637,28 +21985,28 @@
         <v>0.1692</v>
       </c>
       <c r="I12" t="n">
-        <v>1.201134412648232</v>
+        <v>1.274546842052521</v>
       </c>
       <c r="J12" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K12" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2262215516555182</v>
+        <v>0.2492163697908296</v>
       </c>
       <c r="M12" t="n">
-        <v>14.48417816727636</v>
+        <v>14.53800109772094</v>
       </c>
       <c r="N12" t="n">
-        <v>282.4604036770036</v>
+        <v>285.8342605780169</v>
       </c>
       <c r="O12" t="n">
-        <v>16.80655835312524</v>
+        <v>16.90663362642064</v>
       </c>
       <c r="P12" t="n">
-        <v>347.353750191165</v>
+        <v>346.6190072563187</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21715,28 +22063,28 @@
         <v>0.1283</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6521118536374789</v>
+        <v>0.7204102118725587</v>
       </c>
       <c r="J13" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K13" t="n">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1075872583724194</v>
+        <v>0.1284872821191652</v>
       </c>
       <c r="M13" t="n">
-        <v>12.26450958173389</v>
+        <v>12.34337591005185</v>
       </c>
       <c r="N13" t="n">
-        <v>200.8837293970891</v>
+        <v>204.5239619145567</v>
       </c>
       <c r="O13" t="n">
-        <v>14.17334573758395</v>
+        <v>14.30118743022959</v>
       </c>
       <c r="P13" t="n">
-        <v>363.8675027343133</v>
+        <v>363.1792234171645</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21774,7 +22122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N347"/>
+  <dimension ref="A1:N353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46553,7 +46901,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>-44.405900771611286,167.9181053492385</t>
+          <t>-44.40587175787764,167.91807110478862</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -46614,6 +46962,438 @@
       <c r="N347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-44.405856325036986,167.91805288966944</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-44.405460449015195,167.91875957154556</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-44.405063883510024,167.9194654439266</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-44.40462241846111,167.9200776718848</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-44.404233963569766,167.9205202374031</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-44.40380445091181,167.9209636396708</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-44.403255459954735,167.9214302967863</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-44.40270916355134,167.92184209525095</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-44.40214509833867,167.92218071953275</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-44.40154055802585,167.92245894126327</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-44.40095053529138,167.92268825070295</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-44.4003561314426,167.9228545006171</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-29 22:32:59+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-44.405839246023774,167.91803273161528</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-44.40544823998085,167.91874516134902</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-44.40505153735523,167.91945087179784</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-44.40461128555697,167.9200636392716</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-44.404231052639055,167.92051482291672</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-44.40380138986157,167.9209555480115</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-44.40325466324989,167.92142819075164</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-44.40270839061845,167.9218398324008</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-44.40214413951862,167.9221774752224</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-44.40154052483687,167.92245882480066</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-44.400951991196905,167.92269444312</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-44.40035719705446,167.92286020021936</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-30 22:26:37+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-44.405825459348215,167.91801645945955</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-44.405432738620384,167.91872686526537</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-44.40503864248072,167.91943565202536</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-44.404597752743356,167.9200465816711</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-44.40421622845121,167.92048724915182</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-44.40379560321719,167.92094025145252</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-44.40325306984009,167.9214239786825</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-44.40270483512666,167.9218294232909</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-44.40214335191638,167.9221748102533</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-44.40153826798457,167.92245090534422</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-44.40095182320782,167.92269372861034</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-44.400357786541754,167.9228633531909</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-44.40581901184751,167.9180088495983</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-44.405434316192576,167.91872872725574</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-44.40503980850667,167.91943702828112</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-44.40459301959128,167.92004061571416</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-44.40421073002364,167.92047702179536</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-44.40378960690976,167.9209244006737</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-44.403252860180885,167.9214234244629</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-44.40270085452067,167.9218177696151</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-44.402140509699095,167.92216519319143</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-44.40153806885051,167.9224502065687</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-44.40095151522782,167.92269241867595</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-44.400356947655965,167.92285886626985</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-14 22:32:56+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-44.40581860030491,167.91800836386253</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-44.405440763661296,167.91873633713047</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-44.40503610465947,167.9194326566454</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-44.404589353064814,167.9200359941989</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-44.40420889721426,167.920473612677</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-44.40378813928176,167.920920521113</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-44.40325659211419,167.9214332895725</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-44.402701125047315,167.9218185616124</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-44.402142804019135,167.92217295636178</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-44.40154274849963,167.92246662779516</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-44.40095280314405,167.92269789658351</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-44.400359169569306,167.92287075054756</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-44.40581860030491,167.91800836386253</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-44.40544823998085,167.91874516134902</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-44.40503706491617,167.91943379003237</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-44.404584886568756,167.92003036435378</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-44.40420593237537,167.9204680979271</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-44.40378428151612,167.9209103234115</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-44.40325231506698,167.92142198349194</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-44.40269799466712,167.92180939707234</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-44.402140475455504,167.92216507732323</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-44.40154135456183,167.9224617363657</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-44.400950927265974,167.92268991789214</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-44.400359169569306,167.92287075054756</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0461/nzd0461.xlsx
+++ b/data/nzd0461/nzd0461.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N353"/>
+  <dimension ref="A1:N355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17324,6 +17324,102 @@
       <c r="N353" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>434.68</v>
+      </c>
+      <c r="C354" t="n">
+        <v>425.04</v>
+      </c>
+      <c r="D354" t="n">
+        <v>419.77</v>
+      </c>
+      <c r="E354" t="n">
+        <v>425.89</v>
+      </c>
+      <c r="F354" t="n">
+        <v>430.17</v>
+      </c>
+      <c r="G354" t="n">
+        <v>416.07</v>
+      </c>
+      <c r="H354" t="n">
+        <v>404.82</v>
+      </c>
+      <c r="I354" t="n">
+        <v>402.99</v>
+      </c>
+      <c r="J354" t="n">
+        <v>398.31</v>
+      </c>
+      <c r="K354" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="L354" t="n">
+        <v>402.27</v>
+      </c>
+      <c r="M354" t="n">
+        <v>402.38</v>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:31+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>435.8</v>
+      </c>
+      <c r="C355" t="n">
+        <v>425.91</v>
+      </c>
+      <c r="D355" t="n">
+        <v>419.77</v>
+      </c>
+      <c r="E355" t="n">
+        <v>425.89</v>
+      </c>
+      <c r="F355" t="n">
+        <v>430.17</v>
+      </c>
+      <c r="G355" t="n">
+        <v>414.74</v>
+      </c>
+      <c r="H355" t="n">
+        <v>404.43</v>
+      </c>
+      <c r="I355" t="n">
+        <v>402.57</v>
+      </c>
+      <c r="J355" t="n">
+        <v>397.76</v>
+      </c>
+      <c r="K355" t="n">
+        <v>397.49</v>
+      </c>
+      <c r="L355" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="M355" t="n">
+        <v>401.89</v>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17338,7 +17434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21021,6 +21117,26 @@
       </c>
       <c r="B368" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -21189,28 +21305,28 @@
         <v>0.1696</v>
       </c>
       <c r="I2" t="n">
-        <v>1.033479008884517</v>
+        <v>1.08038222191141</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1453527988358443</v>
+        <v>0.1545414795706672</v>
       </c>
       <c r="M2" t="n">
-        <v>15.95155951083258</v>
+        <v>16.07062075929297</v>
       </c>
       <c r="N2" t="n">
-        <v>365.6514048568629</v>
+        <v>374.1829393374701</v>
       </c>
       <c r="O2" t="n">
-        <v>19.1220136193044</v>
+        <v>19.34380881154149</v>
       </c>
       <c r="P2" t="n">
-        <v>364.2764129388156</v>
+        <v>363.8051163416328</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21271,28 +21387,28 @@
         <v>0.1201</v>
       </c>
       <c r="I3" t="n">
-        <v>1.162802422850837</v>
+        <v>1.206755143803267</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1780713888906282</v>
+        <v>0.1871381791683268</v>
       </c>
       <c r="M3" t="n">
-        <v>15.92710120302813</v>
+        <v>16.03837115382668</v>
       </c>
       <c r="N3" t="n">
-        <v>362.5806137735648</v>
+        <v>369.8458085194831</v>
       </c>
       <c r="O3" t="n">
-        <v>19.04154966838479</v>
+        <v>19.23137562733054</v>
       </c>
       <c r="P3" t="n">
-        <v>353.7765103076541</v>
+        <v>353.3341160477185</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21353,28 +21469,28 @@
         <v>0.1062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.386131823915293</v>
+        <v>1.421947665941725</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2491420904991236</v>
+        <v>0.257603926381528</v>
       </c>
       <c r="M4" t="n">
-        <v>15.64278259784382</v>
+        <v>15.7172360252558</v>
       </c>
       <c r="N4" t="n">
-        <v>336.2481198813605</v>
+        <v>340.52909241552</v>
       </c>
       <c r="O4" t="n">
-        <v>18.33706955544861</v>
+        <v>18.45343036986674</v>
       </c>
       <c r="P4" t="n">
-        <v>349.7881077575113</v>
+        <v>349.4270736223539</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21435,28 +21551,28 @@
         <v>0.1328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.291637345515896</v>
+        <v>1.326755489814307</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2270952527120869</v>
+        <v>0.2355815760524685</v>
       </c>
       <c r="M5" t="n">
-        <v>15.45944606214228</v>
+        <v>15.52531551910825</v>
       </c>
       <c r="N5" t="n">
-        <v>330.9184203312223</v>
+        <v>334.9943995903054</v>
       </c>
       <c r="O5" t="n">
-        <v>18.19116324843528</v>
+        <v>18.30285222554959</v>
       </c>
       <c r="P5" t="n">
-        <v>359.14629033991</v>
+        <v>358.7924829914126</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21517,28 +21633,28 @@
         <v>0.1398</v>
       </c>
       <c r="I6" t="n">
-        <v>1.337620689240584</v>
+        <v>1.369475820239916</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2567527300659042</v>
+        <v>0.2650183302806929</v>
       </c>
       <c r="M6" t="n">
-        <v>14.6273404382409</v>
+        <v>14.67954806363481</v>
       </c>
       <c r="N6" t="n">
-        <v>301.718177912334</v>
+        <v>304.9008893068786</v>
       </c>
       <c r="O6" t="n">
-        <v>17.37003678500233</v>
+        <v>17.46141143512971</v>
       </c>
       <c r="P6" t="n">
-        <v>365.2702375239318</v>
+        <v>364.9488272482257</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21595,28 +21711,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.314414252843027</v>
+        <v>1.342575103331438</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.246608562182879</v>
+        <v>0.2544733241409454</v>
       </c>
       <c r="M7" t="n">
-        <v>15.21662978237187</v>
+        <v>15.25345279733476</v>
       </c>
       <c r="N7" t="n">
-        <v>306.7768667107202</v>
+        <v>308.8659084593918</v>
       </c>
       <c r="O7" t="n">
-        <v>17.51504686578715</v>
+        <v>17.57458131675949</v>
       </c>
       <c r="P7" t="n">
-        <v>354.5038199436373</v>
+        <v>354.219200277536</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21673,28 +21789,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.316821737130574</v>
+        <v>1.340281719471646</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2390964583703701</v>
+        <v>0.2462871970637301</v>
       </c>
       <c r="M8" t="n">
-        <v>15.86739229243819</v>
+        <v>15.87510759607602</v>
       </c>
       <c r="N8" t="n">
-        <v>322.4099261941785</v>
+        <v>323.2355910921144</v>
       </c>
       <c r="O8" t="n">
-        <v>17.95577695880015</v>
+        <v>17.97875388040324</v>
       </c>
       <c r="P8" t="n">
-        <v>348.0074183335261</v>
+        <v>347.7719209295019</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21751,28 +21867,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.349779614527609</v>
+        <v>1.375659405362974</v>
       </c>
       <c r="J9" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2446211473984454</v>
+        <v>0.2521260813069324</v>
       </c>
       <c r="M9" t="n">
-        <v>15.9946559978947</v>
+        <v>16.01531770212318</v>
       </c>
       <c r="N9" t="n">
-        <v>328.7754555237232</v>
+        <v>330.1425170486285</v>
       </c>
       <c r="O9" t="n">
-        <v>18.13216632186356</v>
+        <v>18.16982435381885</v>
       </c>
       <c r="P9" t="n">
-        <v>343.0386583862498</v>
+        <v>342.778939255783</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21829,28 +21945,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.467942079607077</v>
+        <v>1.494526124961734</v>
       </c>
       <c r="J10" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K10" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2760844729678806</v>
+        <v>0.283657661018422</v>
       </c>
       <c r="M10" t="n">
-        <v>15.87907232219422</v>
+        <v>15.90197475520928</v>
       </c>
       <c r="N10" t="n">
-        <v>331.9403248283732</v>
+        <v>333.4815787603692</v>
       </c>
       <c r="O10" t="n">
-        <v>18.21922953443348</v>
+        <v>18.26147800043494</v>
       </c>
       <c r="P10" t="n">
-        <v>334.4983044714687</v>
+        <v>334.2320784523384</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21907,28 +22023,28 @@
         <v>0.1806</v>
       </c>
       <c r="I11" t="n">
-        <v>1.471096301593646</v>
+        <v>1.49811069290066</v>
       </c>
       <c r="J11" t="n">
+        <v>354</v>
+      </c>
+      <c r="K11" t="n">
         <v>352</v>
       </c>
-      <c r="K11" t="n">
-        <v>350</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2703245596038756</v>
+        <v>0.2779151139501567</v>
       </c>
       <c r="M11" t="n">
-        <v>15.8704051245337</v>
+        <v>15.89379833094975</v>
       </c>
       <c r="N11" t="n">
-        <v>340.4793869395606</v>
+        <v>342.0631351318077</v>
       </c>
       <c r="O11" t="n">
-        <v>18.4520835392527</v>
+        <v>18.49494890860225</v>
       </c>
       <c r="P11" t="n">
-        <v>333.6492253533823</v>
+        <v>333.3778407471343</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21985,28 +22101,28 @@
         <v>0.1692</v>
       </c>
       <c r="I12" t="n">
-        <v>1.274546842052521</v>
+        <v>1.298159773729018</v>
       </c>
       <c r="J12" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K12" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2492163697908296</v>
+        <v>0.2566511994685147</v>
       </c>
       <c r="M12" t="n">
-        <v>14.53800109772094</v>
+        <v>14.55237861341603</v>
       </c>
       <c r="N12" t="n">
-        <v>285.8342605780169</v>
+        <v>286.902486489229</v>
       </c>
       <c r="O12" t="n">
-        <v>16.90663362642064</v>
+        <v>16.93819608131955</v>
       </c>
       <c r="P12" t="n">
-        <v>346.6190072563187</v>
+        <v>346.3819048990446</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22063,28 +22179,28 @@
         <v>0.1283</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7204102118725587</v>
+        <v>0.7419172396206688</v>
       </c>
       <c r="J13" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K13" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1284872821191652</v>
+        <v>0.1353514680048182</v>
       </c>
       <c r="M13" t="n">
-        <v>12.34337591005185</v>
+        <v>12.36351312780361</v>
       </c>
       <c r="N13" t="n">
-        <v>204.5239619145567</v>
+        <v>205.5849501347269</v>
       </c>
       <c r="O13" t="n">
-        <v>14.30118743022959</v>
+        <v>14.33823385688513</v>
       </c>
       <c r="P13" t="n">
-        <v>363.1792234171645</v>
+        <v>362.9617687780624</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22122,7 +22238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N353"/>
+  <dimension ref="A1:N355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47397,6 +47513,150 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-44.40580385336013,167.9179909583353</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-44.405435482224185,167.91873010350955</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-44.405037133505935,167.91943387098857</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-44.404576286896514,167.92001952480368</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-44.404197576919,167.92045255636242</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-44.403780297952885,167.9208997931777</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-44.40324791222317,167.9214103448814</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-44.40269544398644,167.92180192967007</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-44.4021379756734,167.92215661894434</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-44.401539661922804,167.9224557967731</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-44.400949471360235,167.9226837254753</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-44.400356652912265,167.92285728978413</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:31+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-44.40579617122986,167.91798189127337</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-44.40542951488582,167.9187230603288</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-44.405037133505935,167.91943387098857</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-44.404576286896514,167.92001952480368</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-44.404197576919,167.92045255636242</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-44.403785874941164,167.92091453550543</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-44.403249547565274,167.92141466779367</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-44.40269706714692,167.92180668165327</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-44.402139859070935,167.92216299169547</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-44.40154069078185,167.92245940711365</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-44.400949527356616,167.9226839636452</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-44.40035776386916,167.92286323192278</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0461/nzd0461.xlsx
+++ b/data/nzd0461/nzd0461.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N355"/>
+  <dimension ref="A1:N356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17337,7 +17337,7 @@
         <v>434.68</v>
       </c>
       <c r="C354" t="n">
-        <v>425.04</v>
+        <v>423.18</v>
       </c>
       <c r="D354" t="n">
         <v>419.77</v>
@@ -17385,7 +17385,7 @@
         <v>435.8</v>
       </c>
       <c r="C355" t="n">
-        <v>425.91</v>
+        <v>424.21</v>
       </c>
       <c r="D355" t="n">
         <v>419.77</v>
@@ -17418,6 +17418,54 @@
         <v>401.89</v>
       </c>
       <c r="N355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>435.8</v>
+      </c>
+      <c r="C356" t="n">
+        <v>424.21</v>
+      </c>
+      <c r="D356" t="n">
+        <v>420.48</v>
+      </c>
+      <c r="E356" t="n">
+        <v>426.4</v>
+      </c>
+      <c r="F356" t="n">
+        <v>430.95</v>
+      </c>
+      <c r="G356" t="n">
+        <v>415.43</v>
+      </c>
+      <c r="H356" t="n">
+        <v>405.07</v>
+      </c>
+      <c r="I356" t="n">
+        <v>402.86</v>
+      </c>
+      <c r="J356" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="K356" t="n">
+        <v>397.51</v>
+      </c>
+      <c r="L356" t="n">
+        <v>402.2</v>
+      </c>
+      <c r="M356" t="n">
+        <v>402.31</v>
+      </c>
+      <c r="N356" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17434,7 +17482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21137,6 +21185,16 @@
       </c>
       <c r="B370" t="n">
         <v>0.85</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -21305,28 +21363,28 @@
         <v>0.1696</v>
       </c>
       <c r="I2" t="n">
-        <v>1.08038222191141</v>
+        <v>1.103586339747733</v>
       </c>
       <c r="J2" t="n">
+        <v>355</v>
+      </c>
+      <c r="K2" t="n">
         <v>354</v>
       </c>
-      <c r="K2" t="n">
-        <v>353</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1545414795706672</v>
+        <v>0.1590975715537959</v>
       </c>
       <c r="M2" t="n">
-        <v>16.07062075929297</v>
+        <v>16.12806110667361</v>
       </c>
       <c r="N2" t="n">
-        <v>374.1829393374701</v>
+        <v>378.3971821694295</v>
       </c>
       <c r="O2" t="n">
-        <v>19.34380881154149</v>
+        <v>19.45243383665472</v>
       </c>
       <c r="P2" t="n">
-        <v>363.8051163416328</v>
+        <v>363.5714599096686</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21387,28 +21445,28 @@
         <v>0.1201</v>
       </c>
       <c r="I3" t="n">
-        <v>1.206755143803267</v>
+        <v>1.225646383336688</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1871381791683268</v>
+        <v>0.1913934354063518</v>
       </c>
       <c r="M3" t="n">
-        <v>16.03837115382668</v>
+        <v>16.07937508579271</v>
       </c>
       <c r="N3" t="n">
-        <v>369.8458085194831</v>
+        <v>372.25203229932</v>
       </c>
       <c r="O3" t="n">
-        <v>19.23137562733054</v>
+        <v>19.29383404871411</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3341160477185</v>
+        <v>353.143527703456</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21469,28 +21527,28 @@
         <v>0.1062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.421947665941725</v>
+        <v>1.439806415235286</v>
       </c>
       <c r="J4" t="n">
+        <v>355</v>
+      </c>
+      <c r="K4" t="n">
         <v>354</v>
       </c>
-      <c r="K4" t="n">
-        <v>353</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.257603926381528</v>
+        <v>0.2617892392266437</v>
       </c>
       <c r="M4" t="n">
-        <v>15.7172360252558</v>
+        <v>15.75354593878933</v>
       </c>
       <c r="N4" t="n">
-        <v>340.52909241552</v>
+        <v>342.6914427767931</v>
       </c>
       <c r="O4" t="n">
-        <v>18.45343036986674</v>
+        <v>18.51192704114818</v>
       </c>
       <c r="P4" t="n">
-        <v>349.4270736223539</v>
+        <v>349.2466698420923</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21551,28 +21609,28 @@
         <v>0.1328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.326755489814307</v>
+        <v>1.344165279002858</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2355815760524685</v>
+        <v>0.2397783161444066</v>
       </c>
       <c r="M5" t="n">
-        <v>15.52531551910825</v>
+        <v>15.55692960244687</v>
       </c>
       <c r="N5" t="n">
-        <v>334.9943995903054</v>
+        <v>337.0190463891713</v>
       </c>
       <c r="O5" t="n">
-        <v>18.30285222554959</v>
+        <v>18.35807850482101</v>
       </c>
       <c r="P5" t="n">
-        <v>358.7924829914126</v>
+        <v>358.6167074515587</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21633,28 +21691,28 @@
         <v>0.1398</v>
       </c>
       <c r="I6" t="n">
-        <v>1.369475820239916</v>
+        <v>1.385436435939511</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2650183302806929</v>
+        <v>0.2691155311301365</v>
       </c>
       <c r="M6" t="n">
-        <v>14.67954806363481</v>
+        <v>14.70531737922563</v>
       </c>
       <c r="N6" t="n">
-        <v>304.9008893068786</v>
+        <v>306.5345328090553</v>
       </c>
       <c r="O6" t="n">
-        <v>17.46141143512971</v>
+        <v>17.50812762145214</v>
       </c>
       <c r="P6" t="n">
-        <v>364.9488272482257</v>
+        <v>364.7874427612865</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21711,28 +21769,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.342575103331438</v>
+        <v>1.356323992218319</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2544733241409454</v>
+        <v>0.258345150708469</v>
       </c>
       <c r="M7" t="n">
-        <v>15.25345279733476</v>
+        <v>15.2700176525968</v>
       </c>
       <c r="N7" t="n">
-        <v>308.8659084593918</v>
+        <v>309.8449590064523</v>
       </c>
       <c r="O7" t="n">
-        <v>17.57458131675949</v>
+        <v>17.60241344266326</v>
       </c>
       <c r="P7" t="n">
-        <v>354.219200277536</v>
+        <v>354.0799432024726</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21789,28 +21847,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.340281719471646</v>
+        <v>1.351955535933768</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2462871970637301</v>
+        <v>0.2498651183069911</v>
       </c>
       <c r="M8" t="n">
-        <v>15.87510759607602</v>
+        <v>15.87844450200921</v>
       </c>
       <c r="N8" t="n">
-        <v>323.2355910921144</v>
+        <v>323.6566576496236</v>
       </c>
       <c r="O8" t="n">
-        <v>17.97875388040324</v>
+        <v>17.99046018448732</v>
       </c>
       <c r="P8" t="n">
-        <v>347.7719209295019</v>
+        <v>347.654485403319</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21867,28 +21925,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.375659405362974</v>
+        <v>1.388319214011521</v>
       </c>
       <c r="J9" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2521260813069324</v>
+        <v>0.2558269478488925</v>
       </c>
       <c r="M9" t="n">
-        <v>16.01531770212318</v>
+        <v>16.02408237568848</v>
       </c>
       <c r="N9" t="n">
-        <v>330.1425170486285</v>
+        <v>330.7797950091673</v>
       </c>
       <c r="O9" t="n">
-        <v>18.16982435381885</v>
+        <v>18.18735261133866</v>
       </c>
       <c r="P9" t="n">
-        <v>342.778939255783</v>
+        <v>342.6516186949169</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21945,28 +22003,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.494526124961734</v>
+        <v>1.50733039585152</v>
       </c>
       <c r="J10" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L10" t="n">
-        <v>0.283657661018422</v>
+        <v>0.2873637618426432</v>
       </c>
       <c r="M10" t="n">
-        <v>15.90197475520928</v>
+        <v>15.91158933379585</v>
       </c>
       <c r="N10" t="n">
-        <v>333.4815787603692</v>
+        <v>334.1514776604964</v>
       </c>
       <c r="O10" t="n">
-        <v>18.26147800043494</v>
+        <v>18.27981065712926</v>
       </c>
       <c r="P10" t="n">
-        <v>334.2320784523384</v>
+        <v>334.1035730022701</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22023,28 +22081,28 @@
         <v>0.1806</v>
       </c>
       <c r="I11" t="n">
-        <v>1.49811069290066</v>
+        <v>1.511209419217505</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2779151139501567</v>
+        <v>0.2816402259106832</v>
       </c>
       <c r="M11" t="n">
-        <v>15.89379833094975</v>
+        <v>15.90340542762609</v>
       </c>
       <c r="N11" t="n">
-        <v>342.0631351318077</v>
+        <v>342.7745276700243</v>
       </c>
       <c r="O11" t="n">
-        <v>18.49494890860225</v>
+        <v>18.51417099602422</v>
       </c>
       <c r="P11" t="n">
-        <v>333.3778407471343</v>
+        <v>333.2459717163012</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22101,28 +22159,28 @@
         <v>0.1692</v>
       </c>
       <c r="I12" t="n">
-        <v>1.298159773729018</v>
+        <v>1.309636455597546</v>
       </c>
       <c r="J12" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2566511994685147</v>
+        <v>0.2603067551331849</v>
       </c>
       <c r="M12" t="n">
-        <v>14.55237861341603</v>
+        <v>14.55863391768401</v>
       </c>
       <c r="N12" t="n">
-        <v>286.902486489229</v>
+        <v>287.381697579466</v>
       </c>
       <c r="O12" t="n">
-        <v>16.93819608131955</v>
+        <v>16.95233605080627</v>
       </c>
       <c r="P12" t="n">
-        <v>346.3819048990446</v>
+        <v>346.2664186928449</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22179,28 +22237,28 @@
         <v>0.1283</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7419172396206688</v>
+        <v>0.7525040179990771</v>
       </c>
       <c r="J13" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1353514680048182</v>
+        <v>0.138775929739529</v>
       </c>
       <c r="M13" t="n">
-        <v>12.36351312780361</v>
+        <v>12.37317758766518</v>
       </c>
       <c r="N13" t="n">
-        <v>205.5849501347269</v>
+        <v>206.0965346297055</v>
       </c>
       <c r="O13" t="n">
-        <v>14.33823385688513</v>
+        <v>14.35606264369536</v>
       </c>
       <c r="P13" t="n">
-        <v>362.9617687780624</v>
+        <v>362.854497822433</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22238,7 +22296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N355"/>
+  <dimension ref="A1:N356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47526,7 +47584,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-44.405435482224185,167.91873010350955</t>
+          <t>-44.40544823998085,167.91874516134902</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -47598,7 +47656,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-44.40542951488582,167.9187230603288</t>
+          <t>-44.40544117520184,167.91873682286723</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -47652,6 +47710,78 @@
         </is>
       </c>
       <c r="N355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-44.40579617122986,167.91798189127337</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-44.40544117520184,167.91873682286723</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-44.405032263632584,167.91942812309782</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-44.40457288702586,167.920015239401</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-44.404193372237,167.9204447354477</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-44.403782981616644,167.92090688722976</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-44.403246863926846,167.92140757378394</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-44.402695946393266,167.92180340052198</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-44.40213989331451,167.92216310756368</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-44.40154062440385,167.92245917418848</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-44.40094966734757,167.92268455906986</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-44.400356811620405,167.92285813866104</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
